--- a/Building Agentic Platforms - programme.xlsx
+++ b/Building Agentic Platforms - programme.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Workflows, ReAct loops and multi-agent systems. Task boundaries, success criteria and cost constraints. Typed messages, tool dispatch, state transitions, termination and bounded iteration. The target platform blueprint built across the course: agent runtime, MCP tool gateway, agent identity and credentials, agent registry, platform console, operations.</t>
+          <t>Agents versus hard-coded sequences, ReAct loops and multi-agent systems. Task boundaries, success criteria and cost constraints. Typed messages, tool dispatch, state transitions, termination and bounded iteration. The target platform blueprint built across the course: agent runtime, MCP tool gateway, agent identity and credentials, agent registry, platform console, operations.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Refresh 2025 LLM/prompting/RAG basics and HTTP, JSON, async programming and tests. Set up your repository, mock data, five acceptance scenarios and a workflow baseline. Mentor prepares a staged reference repository with runnable checkpoints and checks for each demo. Read the architecture, ReAct and chosen model API tool-calling references.</t>
+          <t>Refresh 2025 LLM/prompting/RAG basics and HTTP, JSON, async programming and tests. Read the architecture, ReAct and chosen model API tool-calling references. Nothing needs to be set up before this session.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Replay the demo in your own repository, run its checks and commit the checkpoint. Test missing evidence, tool failures, repeated actions and budget exhaustion. Compare against the workflow baseline. Record observable events without requiring hidden model reasoning.</t>
+          <t>Replay the demo in your own repository, run its checks and commit the checkpoint. Test missing evidence, tool failures, repeated actions and budget exhaustion. Write INC-001 as a hard-coded sequence and compare it with the agent loop on all three tickets. Record observable events without requiring hidden model reasoning.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">

--- a/Building Agentic Platforms - programme.xlsx
+++ b/Building Agentic Platforms - programme.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Programme" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sessions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sessions'!$A$1:$M$13</definedName>
@@ -488,7 +488,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
